--- a/templates/b2b-calculators.xlsx
+++ b/templates/b2b-calculators.xlsx
@@ -19,7 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="$#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -93,13 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -467,7 +477,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -514,7 +524,7 @@
           <t>Price per unit per year</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>900</v>
       </c>
     </row>
@@ -541,13 +551,14 @@
           <t>Opportunity per year</t>
         </is>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="6">
         <f>B5*B6*B7</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -555,9 +566,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -602,7 +613,7 @@
           <t>Cost per hour</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>8000</v>
       </c>
     </row>
@@ -612,7 +623,7 @@
           <t>Reduction your product delivers (0-1)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="7" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -622,63 +633,95 @@
           <t>Your yearly cost to the customer</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="8" t="n">
         <v>36000</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>One-off setup cost</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>14000</v>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Months to reach full effect</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Value per month</t>
-        </is>
-      </c>
-      <c r="B11" s="5">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Value per month at full effect</t>
+        </is>
+      </c>
+      <c r="B13" s="6">
         <f>B5*B6*B7</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Value per year</t>
-        </is>
-      </c>
-      <c r="B12" s="5">
-        <f>B11*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ROI (one year)</t>
-        </is>
-      </c>
-      <c r="B13" s="5">
-        <f>(B12-B8)/B8</f>
-        <v/>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Payback (months)</t>
-        </is>
-      </c>
-      <c r="B14" s="5">
-        <f>B8/B11</f>
+          <t>Year-one value, after ramp-up</t>
+        </is>
+      </c>
+      <c r="B14" s="6">
+        <f>B13*(12-B10/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Year-one cost</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>B8+B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ROI (one year)</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>(B14-B15)/B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Payback at full effect (months)</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <f>B15/B13</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -686,7 +729,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -718,95 +761,96 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Champion / economic / technical / user / other</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>What they fear</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>What they need</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Message and proof</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
+      <c r="A7" s="12" t="inlineStr"/>
+      <c r="B7" s="12" t="inlineStr"/>
+      <c r="C7" s="12" t="inlineStr"/>
+      <c r="D7" s="12" t="inlineStr"/>
+      <c r="E7" s="12" t="inlineStr"/>
+      <c r="F7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr"/>
-      <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" s="12" t="inlineStr"/>
+      <c r="C8" s="12" t="inlineStr"/>
+      <c r="D8" s="12" t="inlineStr"/>
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="12" t="inlineStr"/>
+      <c r="C9" s="12" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr"/>
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
-      <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="B10" s="12" t="inlineStr"/>
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr"/>
+      <c r="E10" s="12" t="inlineStr"/>
+      <c r="F10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="B11" s="12" t="inlineStr"/>
+      <c r="C11" s="12" t="inlineStr"/>
+      <c r="D11" s="12" t="inlineStr"/>
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr"/>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="B12" s="12" t="inlineStr"/>
+      <c r="C12" s="12" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr"/>
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="B13" s="12" t="inlineStr"/>
+      <c r="C13" s="12" t="inlineStr"/>
+      <c r="D13" s="12" t="inlineStr"/>
+      <c r="E13" s="12" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -814,7 +858,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -846,97 +890,98 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Deal segment</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Typical deal value</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>People who must say yes</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Cost per deal</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Gross profit per deal</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Route pays?</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="8" t="n">
+      <c r="A7" s="12" t="inlineStr"/>
+      <c r="B7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="8" t="n">
+      <c r="C7" s="12" t="inlineStr"/>
+      <c r="D7" s="12" t="inlineStr"/>
+      <c r="E7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="14">
         <f>IF(F7&gt;E7,"yes","no")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr"/>
-      <c r="B8" s="8" t="n">
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="8" t="n">
+      <c r="C8" s="12" t="inlineStr"/>
+      <c r="D8" s="12" t="inlineStr"/>
+      <c r="E8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="14">
         <f>IF(F8&gt;E8,"yes","no")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="8" t="n">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="8" t="n">
+      <c r="C9" s="12" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr"/>
+      <c r="E9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="14">
         <f>IF(F9&gt;E9,"yes","no")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>